--- a/sub member.xlsx
+++ b/sub member.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Peter\Code\Auto_Photo-main\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBC2777-A1B3-492F-BB53-066D01C4F111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -14,19 +20,89 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>謝竣翔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/hsieh1010#</t>
+  </si>
+  <si>
+    <t>Yu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/LG.YU22#</t>
+  </si>
+  <si>
+    <t>慕容煙雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/shi.shang.514952#</t>
+  </si>
+  <si>
+    <t>用戶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聯絡方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尺寸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,11 +125,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +415,61 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2556</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/sub member.xlsx
+++ b/sub member.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Peter\Code\Auto_Photo-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBC2777-A1B3-492F-BB53-066D01C4F111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D068413-EADE-48C0-9D7C-C6BDEEC18D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>謝竣翔</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -60,6 +60,14 @@
   </si>
   <si>
     <t>尺寸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>開始日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>期數</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -125,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -134,6 +142,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -416,15 +427,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="48.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="9" style="2"/>
+    <col min="4" max="4" width="14.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="19.8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -434,8 +447,14 @@
       <c r="C1" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="D1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -446,7 +465,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -456,8 +475,14 @@
       <c r="C3" s="2">
         <v>2622</v>
       </c>
+      <c r="D3" s="4">
+        <v>46174</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -466,6 +491,12 @@
       </c>
       <c r="C4" s="2">
         <v>2556</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46174</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
